--- a/artfynd/A 43229-2025 artfynd.xlsx
+++ b/artfynd/A 43229-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>128647139</v>
       </c>
       <c r="B2" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,59 +792,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128647084</v>
+        <v>128647292</v>
       </c>
       <c r="B3" t="n">
-        <v>98572</v>
+        <v>57686</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Blanktjärnen, Blanktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>451125</v>
+        <v>451106</v>
       </c>
       <c r="R3" t="n">
-        <v>6710158</v>
+        <v>6710134</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -876,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +872,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Födohål</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,45 +904,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128647292</v>
+        <v>128647015</v>
       </c>
       <c r="B4" t="n">
-        <v>57682</v>
+        <v>98579</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Blanktjärnen, Blanktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>451106</v>
+        <v>451141</v>
       </c>
       <c r="R4" t="n">
-        <v>6710134</v>
+        <v>6710113</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -983,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,12 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Födohål</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,57 +1020,51 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128647015</v>
+        <v>128677341</v>
       </c>
       <c r="B5" t="n">
-        <v>98572</v>
+        <v>79087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Blanktjärnen, Blanktjärnen, Dlr</t>
+          <t>Blanktjärn, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>451141</v>
+        <v>451034</v>
       </c>
       <c r="R5" t="n">
-        <v>6710113</v>
+        <v>6710184</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1102,27 +1091,18 @@
           <t>2025-09-23</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-23</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1138,6 +1118,1795 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128678222</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57689</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Blanktjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>450905</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6709951</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>kåda</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128677200</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Blanktjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>450805</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6709970</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128677100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57689</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Blanktjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>451158</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6710145</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>ringhack. Hela trädet</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128677209</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Blanktjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>450780</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6710010</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128677238</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78844</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Blanktjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>450787</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6710017</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128677168</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Blanktjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>450878</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6709947</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128677382</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Blanktjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>451175</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6710145</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128677177</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Blanktjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>450862</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6709947</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128647084</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98579</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Blanktjärnen, Blanktjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>451125</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6710158</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128677192</v>
+      </c>
+      <c r="B15" t="n">
+        <v>90491</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Blanktjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>450815</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6709962</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128677415</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Blanktjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>451284</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6710055</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128678087</v>
+      </c>
+      <c r="B17" t="n">
+        <v>56880</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Blanktjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>450906</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6710013</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128677395</v>
+      </c>
+      <c r="B18" t="n">
+        <v>78845</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Blanktjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>451272</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6710087</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128677346</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Blanktjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>451016</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6710181</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128677354</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Blanktjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>451032</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6710168</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128677370</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Blanktjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>451143</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6710142</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128677350</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Blanktjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>451044</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6710170</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43229-2025 artfynd.xlsx
+++ b/artfynd/A 43229-2025 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>128647015</v>
       </c>
       <c r="B4" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128677382</v>
+        <v>128677177</v>
       </c>
       <c r="B12" t="n">
         <v>79087</v>
@@ -1799,10 +1799,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>451175</v>
+        <v>450862</v>
       </c>
       <c r="R12" t="n">
-        <v>6710145</v>
+        <v>6709947</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1862,7 +1862,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128677177</v>
+        <v>128677382</v>
       </c>
       <c r="B13" t="n">
         <v>79087</v>
@@ -1900,10 +1900,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>450862</v>
+        <v>451175</v>
       </c>
       <c r="R13" t="n">
-        <v>6709947</v>
+        <v>6710145</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1966,7 +1966,7 @@
         <v>128647084</v>
       </c>
       <c r="B14" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>128677192</v>
       </c>
       <c r="B15" t="n">
-        <v>90491</v>
+        <v>90497</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2405,10 +2405,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128677395</v>
+        <v>128677354</v>
       </c>
       <c r="B18" t="n">
-        <v>78845</v>
+        <v>79087</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2416,21 +2416,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2443,10 +2443,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>451272</v>
+        <v>451032</v>
       </c>
       <c r="R18" t="n">
-        <v>6710087</v>
+        <v>6710168</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2607,10 +2607,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128677354</v>
+        <v>128677395</v>
       </c>
       <c r="B20" t="n">
-        <v>79087</v>
+        <v>78845</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2618,21 +2618,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2645,10 +2645,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>451032</v>
+        <v>451272</v>
       </c>
       <c r="R20" t="n">
-        <v>6710168</v>
+        <v>6710087</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>

--- a/artfynd/A 43229-2025 artfynd.xlsx
+++ b/artfynd/A 43229-2025 artfynd.xlsx
@@ -2084,10 +2084,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128677192</v>
+        <v>128677415</v>
       </c>
       <c r="B15" t="n">
-        <v>90497</v>
+        <v>79087</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2095,21 +2095,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2122,10 +2122,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>450815</v>
+        <v>451284</v>
       </c>
       <c r="R15" t="n">
-        <v>6709962</v>
+        <v>6710055</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2185,10 +2185,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128677415</v>
+        <v>128677192</v>
       </c>
       <c r="B16" t="n">
-        <v>79087</v>
+        <v>90497</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2196,21 +2196,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2223,10 +2223,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>451284</v>
+        <v>450815</v>
       </c>
       <c r="R16" t="n">
-        <v>6710055</v>
+        <v>6709962</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>

--- a/artfynd/A 43229-2025 artfynd.xlsx
+++ b/artfynd/A 43229-2025 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>128647015</v>
       </c>
       <c r="B4" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>128677341</v>
       </c>
       <c r="B5" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>128677200</v>
       </c>
       <c r="B7" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>128677209</v>
       </c>
       <c r="B9" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>128677238</v>
       </c>
       <c r="B10" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>128677168</v>
       </c>
       <c r="B11" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>128677177</v>
       </c>
       <c r="B12" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>128677382</v>
       </c>
       <c r="B13" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>128647084</v>
       </c>
       <c r="B14" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>128677415</v>
       </c>
       <c r="B15" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>128677192</v>
       </c>
       <c r="B16" t="n">
-        <v>90497</v>
+        <v>90499</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
         <v>128677354</v>
       </c>
       <c r="B18" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>128677346</v>
       </c>
       <c r="B19" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>128677395</v>
       </c>
       <c r="B20" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>128677370</v>
       </c>
       <c r="B21" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>128677350</v>
       </c>
       <c r="B22" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 43229-2025 artfynd.xlsx
+++ b/artfynd/A 43229-2025 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>128647015</v>
       </c>
       <c r="B4" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>128647084</v>
       </c>
       <c r="B14" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 43229-2025 artfynd.xlsx
+++ b/artfynd/A 43229-2025 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>128647015</v>
       </c>
       <c r="B4" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>128647084</v>
       </c>
       <c r="B14" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 43229-2025 artfynd.xlsx
+++ b/artfynd/A 43229-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128647139</v>
       </c>
       <c r="B2" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>128647292</v>
       </c>
       <c r="B3" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>128647015</v>
       </c>
       <c r="B4" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>128677341</v>
       </c>
       <c r="B5" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>128678222</v>
       </c>
       <c r="B6" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>128677200</v>
       </c>
       <c r="B7" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>128677100</v>
       </c>
       <c r="B8" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>128677209</v>
       </c>
       <c r="B9" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>128677238</v>
       </c>
       <c r="B10" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>128677168</v>
       </c>
       <c r="B11" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>128677177</v>
       </c>
       <c r="B12" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>128677382</v>
       </c>
       <c r="B13" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>128647084</v>
       </c>
       <c r="B14" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>128677415</v>
       </c>
       <c r="B15" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>128677192</v>
       </c>
       <c r="B16" t="n">
-        <v>90499</v>
+        <v>90526</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>128678087</v>
       </c>
       <c r="B17" t="n">
-        <v>56880</v>
+        <v>56907</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
         <v>128677354</v>
       </c>
       <c r="B18" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>128677346</v>
       </c>
       <c r="B19" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>128677395</v>
       </c>
       <c r="B20" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>128677370</v>
       </c>
       <c r="B21" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>128677350</v>
       </c>
       <c r="B22" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 43229-2025 artfynd.xlsx
+++ b/artfynd/A 43229-2025 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>128647015</v>
       </c>
       <c r="B4" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>128677341</v>
       </c>
       <c r="B5" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>128677200</v>
       </c>
       <c r="B7" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>128677209</v>
       </c>
       <c r="B9" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>128677238</v>
       </c>
       <c r="B10" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>128677168</v>
       </c>
       <c r="B11" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>128677177</v>
       </c>
       <c r="B12" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>128677382</v>
       </c>
       <c r="B13" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>128647084</v>
       </c>
       <c r="B14" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>128677415</v>
       </c>
       <c r="B15" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>128677192</v>
       </c>
       <c r="B16" t="n">
-        <v>90526</v>
+        <v>90531</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
         <v>128677354</v>
       </c>
       <c r="B18" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>128677346</v>
       </c>
       <c r="B19" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>128677395</v>
       </c>
       <c r="B20" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>128677370</v>
       </c>
       <c r="B21" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>128677350</v>
       </c>
       <c r="B22" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 43229-2025 artfynd.xlsx
+++ b/artfynd/A 43229-2025 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>128647015</v>
       </c>
       <c r="B4" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>128647084</v>
       </c>
       <c r="B14" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>128677192</v>
       </c>
       <c r="B16" t="n">
-        <v>90531</v>
+        <v>90536</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 43229-2025 artfynd.xlsx
+++ b/artfynd/A 43229-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128647139</v>
       </c>
       <c r="B2" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>128647292</v>
       </c>
       <c r="B3" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>128647015</v>
       </c>
       <c r="B4" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>128677341</v>
       </c>
       <c r="B5" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>128678222</v>
       </c>
       <c r="B6" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>128677200</v>
       </c>
       <c r="B7" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>128677100</v>
       </c>
       <c r="B8" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>128677209</v>
       </c>
       <c r="B9" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>128677238</v>
       </c>
       <c r="B10" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>128677168</v>
       </c>
       <c r="B11" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>128677177</v>
       </c>
       <c r="B12" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>128677382</v>
       </c>
       <c r="B13" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>128647084</v>
       </c>
       <c r="B14" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>128677415</v>
       </c>
       <c r="B15" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>128677192</v>
       </c>
       <c r="B16" t="n">
-        <v>90536</v>
+        <v>90540</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>128678087</v>
       </c>
       <c r="B17" t="n">
-        <v>56907</v>
+        <v>56910</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
         <v>128677354</v>
       </c>
       <c r="B18" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>128677346</v>
       </c>
       <c r="B19" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>128677395</v>
       </c>
       <c r="B20" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>128677370</v>
       </c>
       <c r="B21" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>128677350</v>
       </c>
       <c r="B22" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 43229-2025 artfynd.xlsx
+++ b/artfynd/A 43229-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128647139</v>
       </c>
       <c r="B2" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>128647292</v>
       </c>
       <c r="B3" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>128647015</v>
       </c>
       <c r="B4" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>128677341</v>
       </c>
       <c r="B5" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>128678222</v>
       </c>
       <c r="B6" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>128677200</v>
       </c>
       <c r="B7" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>128677100</v>
       </c>
       <c r="B8" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>128677209</v>
       </c>
       <c r="B9" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>128677238</v>
       </c>
       <c r="B10" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>128677168</v>
       </c>
       <c r="B11" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>128677177</v>
       </c>
       <c r="B12" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>128677382</v>
       </c>
       <c r="B13" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>128647084</v>
       </c>
       <c r="B14" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>128677415</v>
       </c>
       <c r="B15" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>128677192</v>
       </c>
       <c r="B16" t="n">
-        <v>90540</v>
+        <v>90545</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>128678087</v>
       </c>
       <c r="B17" t="n">
-        <v>56910</v>
+        <v>56913</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
         <v>128677354</v>
       </c>
       <c r="B18" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>128677346</v>
       </c>
       <c r="B19" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>128677395</v>
       </c>
       <c r="B20" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>128677370</v>
       </c>
       <c r="B21" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>128677350</v>
       </c>
       <c r="B22" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 43229-2025 artfynd.xlsx
+++ b/artfynd/A 43229-2025 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>128647015</v>
       </c>
       <c r="B4" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>128677341</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>128677200</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>128677209</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>128677238</v>
       </c>
       <c r="B10" t="n">
-        <v>78786</v>
+        <v>78791</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>128677168</v>
       </c>
       <c r="B11" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>128677177</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>128677382</v>
       </c>
       <c r="B13" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>128647084</v>
       </c>
       <c r="B14" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>128677415</v>
       </c>
       <c r="B15" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>128677192</v>
       </c>
       <c r="B16" t="n">
-        <v>90547</v>
+        <v>90552</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
         <v>128677354</v>
       </c>
       <c r="B18" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>128677346</v>
       </c>
       <c r="B19" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>128677395</v>
       </c>
       <c r="B20" t="n">
-        <v>78787</v>
+        <v>78792</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>128677370</v>
       </c>
       <c r="B21" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>128677350</v>
       </c>
       <c r="B22" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 43229-2025 artfynd.xlsx
+++ b/artfynd/A 43229-2025 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>128647015</v>
       </c>
       <c r="B4" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>128677341</v>
       </c>
       <c r="B5" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>128677200</v>
       </c>
       <c r="B7" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>128677209</v>
       </c>
       <c r="B9" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>128677238</v>
       </c>
       <c r="B10" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>128677168</v>
       </c>
       <c r="B11" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>128677177</v>
       </c>
       <c r="B12" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>128677382</v>
       </c>
       <c r="B13" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>128647084</v>
       </c>
       <c r="B14" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>128677415</v>
       </c>
       <c r="B15" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>128677192</v>
       </c>
       <c r="B16" t="n">
-        <v>90552</v>
+        <v>90558</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
         <v>128677354</v>
       </c>
       <c r="B18" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>128677346</v>
       </c>
       <c r="B19" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>128677395</v>
       </c>
       <c r="B20" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>128677370</v>
       </c>
       <c r="B21" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>128677350</v>
       </c>
       <c r="B22" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 43229-2025 artfynd.xlsx
+++ b/artfynd/A 43229-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128647139</v>
       </c>
       <c r="B2" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>128647292</v>
       </c>
       <c r="B3" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>128647015</v>
       </c>
       <c r="B4" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>128677341</v>
       </c>
       <c r="B5" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>128678222</v>
       </c>
       <c r="B6" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>128677200</v>
       </c>
       <c r="B7" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>128677100</v>
       </c>
       <c r="B8" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>128677209</v>
       </c>
       <c r="B9" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>128677238</v>
       </c>
       <c r="B10" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>128677168</v>
       </c>
       <c r="B11" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>128677177</v>
       </c>
       <c r="B12" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>128677382</v>
       </c>
       <c r="B13" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>128647084</v>
       </c>
       <c r="B14" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>128677415</v>
       </c>
       <c r="B15" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>128677192</v>
       </c>
       <c r="B16" t="n">
-        <v>90558</v>
+        <v>90562</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>128678087</v>
       </c>
       <c r="B17" t="n">
-        <v>56913</v>
+        <v>56915</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
         <v>128677354</v>
       </c>
       <c r="B18" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>128677346</v>
       </c>
       <c r="B19" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>128677395</v>
       </c>
       <c r="B20" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>128677370</v>
       </c>
       <c r="B21" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>128677350</v>
       </c>
       <c r="B22" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
